--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/112.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/112.xlsx
@@ -426,13 +426,13 @@
         <v>-14.55696852279757</v>
       </c>
       <c r="E2">
-        <v>-18.06736803696022</v>
+        <v>-12.76616428156901</v>
       </c>
       <c r="F2">
-        <v>1.938438389388934</v>
+        <v>2.133190879256709</v>
       </c>
       <c r="G2">
-        <v>-15.23507973134417</v>
+        <v>-11.83976845766678</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.5034721577223</v>
       </c>
       <c r="E3">
-        <v>-18.808760744548</v>
+        <v>-13.97383131535656</v>
       </c>
       <c r="F3">
-        <v>2.306046305198882</v>
+        <v>1.954160802694069</v>
       </c>
       <c r="G3">
-        <v>-14.68874321681039</v>
+        <v>-9.982560961583918</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.4123205938792</v>
       </c>
       <c r="E4">
-        <v>-19.58119161298434</v>
+        <v>-15.24416790093627</v>
       </c>
       <c r="F4">
-        <v>2.233083704360301</v>
+        <v>2.2383206430808</v>
       </c>
       <c r="G4">
-        <v>-14.08753155291645</v>
+        <v>-10.45282891670509</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.27662087156617</v>
       </c>
       <c r="E5">
-        <v>-19.83893423960491</v>
+        <v>-14.95349873980593</v>
       </c>
       <c r="F5">
-        <v>2.051845200301798</v>
+        <v>1.764618743789903</v>
       </c>
       <c r="G5">
-        <v>-13.60919015214826</v>
+        <v>-9.27712457607578</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.1150625465481</v>
       </c>
       <c r="E6">
-        <v>-19.98831048322192</v>
+        <v>-14.94258058897343</v>
       </c>
       <c r="F6">
-        <v>2.275282396593714</v>
+        <v>2.006982478500982</v>
       </c>
       <c r="G6">
-        <v>-12.39584691901056</v>
+        <v>-8.887325298478425</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.94970524709683</v>
       </c>
       <c r="E7">
-        <v>-20.5479845858299</v>
+        <v>-16.63857561737812</v>
       </c>
       <c r="F7">
-        <v>2.375427045387757</v>
+        <v>2.291859685058538</v>
       </c>
       <c r="G7">
-        <v>-11.91525295964181</v>
+        <v>-8.630861740170667</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.77027049767365</v>
       </c>
       <c r="E8">
-        <v>-20.85773673642856</v>
+        <v>-18.02267199850451</v>
       </c>
       <c r="F8">
-        <v>2.508948273575399</v>
+        <v>2.449572554877535</v>
       </c>
       <c r="G8">
-        <v>-11.20172180054652</v>
+        <v>-8.683059412738313</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.59934243297637</v>
       </c>
       <c r="E9">
-        <v>-22.18424904207342</v>
+        <v>-17.09781269496998</v>
       </c>
       <c r="F9">
-        <v>2.293731795388864</v>
+        <v>2.316281612827872</v>
       </c>
       <c r="G9">
-        <v>-11.51492096083864</v>
+        <v>-6.639580249947334</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.41956421618224</v>
       </c>
       <c r="E10">
-        <v>-22.51989953552194</v>
+        <v>-18.19223165077371</v>
       </c>
       <c r="F10">
-        <v>2.535567031696958</v>
+        <v>2.561107255460072</v>
       </c>
       <c r="G10">
-        <v>-10.39587347287625</v>
+        <v>-6.524947493546573</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.23123641108775</v>
       </c>
       <c r="E11">
-        <v>-23.79747262256591</v>
+        <v>-18.95977629575578</v>
       </c>
       <c r="F11">
-        <v>2.722025907127904</v>
+        <v>2.655454989169324</v>
       </c>
       <c r="G11">
-        <v>-9.598503821715592</v>
+        <v>-5.983312969507474</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.03708001680855</v>
       </c>
       <c r="E12">
-        <v>-24.04857197781722</v>
+        <v>-19.98654890683294</v>
       </c>
       <c r="F12">
-        <v>2.736278796660472</v>
+        <v>2.594450700157558</v>
       </c>
       <c r="G12">
-        <v>-9.30962179440052</v>
+        <v>-6.004601534985151</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.81989561615051</v>
       </c>
       <c r="E13">
-        <v>-25.19793943723003</v>
+        <v>-22.19524870543805</v>
       </c>
       <c r="F13">
-        <v>2.883353772292719</v>
+        <v>3.503154830415365</v>
       </c>
       <c r="G13">
-        <v>-8.893769617621174</v>
+        <v>-5.498177799500453</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.60141479676514</v>
       </c>
       <c r="E14">
-        <v>-26.23568454082777</v>
+        <v>-21.8836127096522</v>
       </c>
       <c r="F14">
-        <v>3.480590102363107</v>
+        <v>3.411956549571556</v>
       </c>
       <c r="G14">
-        <v>-8.878977870831198</v>
+        <v>-5.322553696752735</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.36722057235749</v>
       </c>
       <c r="E15">
-        <v>-27.12325638938314</v>
+        <v>-23.34522750884189</v>
       </c>
       <c r="F15">
-        <v>3.788769283961412</v>
+        <v>2.908223018459566</v>
       </c>
       <c r="G15">
-        <v>-8.654929500309194</v>
+        <v>-5.063921250994183</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.12548705879071</v>
       </c>
       <c r="E16">
-        <v>-28.36605985299621</v>
+        <v>-22.56825005250184</v>
       </c>
       <c r="F16">
-        <v>4.126141789569178</v>
+        <v>3.472646058970259</v>
       </c>
       <c r="G16">
-        <v>-7.902847269111989</v>
+        <v>-6.164633272882389</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.8773645880125</v>
       </c>
       <c r="E17">
-        <v>-29.29239091058323</v>
+        <v>-24.83522225463765</v>
       </c>
       <c r="F17">
-        <v>4.610108817715567</v>
+        <v>3.88244106986998</v>
       </c>
       <c r="G17">
-        <v>-8.318505853819326</v>
+        <v>-4.733348022544806</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.61022197690291</v>
       </c>
       <c r="E18">
-        <v>-30.13091032868752</v>
+        <v>-26.57473591825605</v>
       </c>
       <c r="F18">
-        <v>4.650905912303442</v>
+        <v>4.464975535275483</v>
       </c>
       <c r="G18">
-        <v>-8.785620555021877</v>
+        <v>-5.661064200154408</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.34193855800187</v>
       </c>
       <c r="E19">
-        <v>-30.28178549720107</v>
+        <v>-26.92180722315192</v>
       </c>
       <c r="F19">
-        <v>4.918640883827465</v>
+        <v>4.478108472079466</v>
       </c>
       <c r="G19">
-        <v>-8.690684971642463</v>
+        <v>-5.369727819112872</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.05964129655176</v>
       </c>
       <c r="E20">
-        <v>-31.92991908381869</v>
+        <v>-27.55346142011182</v>
       </c>
       <c r="F20">
-        <v>5.34855528220638</v>
+        <v>5.04279824689386</v>
       </c>
       <c r="G20">
-        <v>-8.920176888731586</v>
+        <v>-4.726562456359875</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.77560139739533</v>
       </c>
       <c r="E21">
-        <v>-30.99039884568433</v>
+        <v>-28.46788711953268</v>
       </c>
       <c r="F21">
-        <v>5.514977606898412</v>
+        <v>5.427697503869846</v>
       </c>
       <c r="G21">
-        <v>-8.769020855152647</v>
+        <v>-4.93488721316902</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.48933810960613</v>
       </c>
       <c r="E22">
-        <v>-31.88882091796208</v>
+        <v>-29.8338718688654</v>
       </c>
       <c r="F22">
-        <v>5.938546710971884</v>
+        <v>5.884066643624566</v>
       </c>
       <c r="G22">
-        <v>-8.876313518924929</v>
+        <v>-6.167707777483589</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.19107776461634</v>
       </c>
       <c r="E23">
-        <v>-31.18195103197178</v>
+        <v>-30.42116739868316</v>
       </c>
       <c r="F23">
-        <v>6.083141554600148</v>
+        <v>5.733008877519659</v>
       </c>
       <c r="G23">
-        <v>-9.676895485992285</v>
+        <v>-6.247257712970766</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.89025793534028</v>
       </c>
       <c r="E24">
-        <v>-32.03104217264698</v>
+        <v>-29.8786856476453</v>
       </c>
       <c r="F24">
-        <v>6.047687429760329</v>
+        <v>5.950847966903456</v>
       </c>
       <c r="G24">
-        <v>-9.030166716625732</v>
+        <v>-5.193365441514278</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.568786835109353</v>
       </c>
       <c r="E25">
-        <v>-33.75707004067053</v>
+        <v>-29.74386618372595</v>
       </c>
       <c r="F25">
-        <v>6.215549456998427</v>
+        <v>6.183592699333228</v>
       </c>
       <c r="G25">
-        <v>-8.863795658675647</v>
+        <v>-6.035579547727869</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.234907480383741</v>
       </c>
       <c r="E26">
-        <v>-32.23932254191876</v>
+        <v>-29.5866828509197</v>
       </c>
       <c r="F26">
-        <v>5.979100265543337</v>
+        <v>5.54746948990582</v>
       </c>
       <c r="G26">
-        <v>-9.781976606433503</v>
+        <v>-5.44401139399714</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.88454336261519</v>
       </c>
       <c r="E27">
-        <v>-32.93414442281166</v>
+        <v>-28.84358743710505</v>
       </c>
       <c r="F27">
-        <v>6.178213281419448</v>
+        <v>5.794581426569747</v>
       </c>
       <c r="G27">
-        <v>-9.007096447841276</v>
+        <v>-4.918947038833238</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.513658799502126</v>
       </c>
       <c r="E28">
-        <v>-32.81876116933322</v>
+        <v>-29.52447746771334</v>
       </c>
       <c r="F28">
-        <v>5.818725022891741</v>
+        <v>5.598947553785393</v>
       </c>
       <c r="G28">
-        <v>-7.913268428784786</v>
+        <v>-6.058009978308233</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.132369407851288</v>
       </c>
       <c r="E29">
-        <v>-31.43545953539518</v>
+        <v>-29.29627634128181</v>
       </c>
       <c r="F29">
-        <v>6.101943837908892</v>
+        <v>5.419705415167636</v>
       </c>
       <c r="G29">
-        <v>-8.950433032731226</v>
+        <v>-5.14194213723466</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.729503456157104</v>
       </c>
       <c r="E30">
-        <v>-32.03797073787872</v>
+        <v>-28.81442406449565</v>
       </c>
       <c r="F30">
-        <v>5.820683283431959</v>
+        <v>6.102633039588021</v>
       </c>
       <c r="G30">
-        <v>-8.005736533551497</v>
+        <v>-5.263117649424953</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.317001687872213</v>
       </c>
       <c r="E31">
-        <v>-31.24246955861029</v>
+        <v>-29.06583588445349</v>
       </c>
       <c r="F31">
-        <v>5.821294618575225</v>
+        <v>5.251538548725308</v>
       </c>
       <c r="G31">
-        <v>-8.315451036547485</v>
+        <v>-4.251490792875672</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.893841166209459</v>
       </c>
       <c r="E32">
-        <v>-30.69995157978037</v>
+        <v>-28.04893987518707</v>
       </c>
       <c r="F32">
-        <v>5.434925837826674</v>
+        <v>5.189407680045734</v>
       </c>
       <c r="G32">
-        <v>-7.887868492693125</v>
+        <v>-4.516980991693463</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.464591402641648</v>
       </c>
       <c r="E33">
-        <v>-30.29021298732935</v>
+        <v>-27.52229193351703</v>
       </c>
       <c r="F33">
-        <v>5.683495701119527</v>
+        <v>5.103008959933746</v>
       </c>
       <c r="G33">
-        <v>-7.790485118030364</v>
+        <v>-3.995558792460543</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.044845951222506</v>
       </c>
       <c r="E34">
-        <v>-30.24077563658761</v>
+        <v>-26.95420845467681</v>
       </c>
       <c r="F34">
-        <v>5.379912301871953</v>
+        <v>4.560685104994938</v>
       </c>
       <c r="G34">
-        <v>-7.349249411267155</v>
+        <v>-4.330676512769752</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.635133402719545</v>
       </c>
       <c r="E35">
-        <v>-29.76166535081309</v>
+        <v>-26.82492957870583</v>
       </c>
       <c r="F35">
-        <v>5.276387914074488</v>
+        <v>4.830457860329846</v>
       </c>
       <c r="G35">
-        <v>-7.712198452843573</v>
+        <v>-4.051336277749544</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.256110211578314</v>
       </c>
       <c r="E36">
-        <v>-29.54824969201661</v>
+        <v>-26.40435208371746</v>
       </c>
       <c r="F36">
-        <v>5.246303266739615</v>
+        <v>4.931242008758852</v>
       </c>
       <c r="G36">
-        <v>-6.741350617835071</v>
+        <v>-3.834460657556487</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.911562323353613</v>
       </c>
       <c r="E37">
-        <v>-27.90008893455494</v>
+        <v>-26.40605478994434</v>
       </c>
       <c r="F37">
-        <v>5.351494329751513</v>
+        <v>4.881375947845126</v>
       </c>
       <c r="G37">
-        <v>-6.853788237012562</v>
+        <v>-3.442715615574382</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.608060157363348</v>
       </c>
       <c r="E38">
-        <v>-27.68747707989482</v>
+        <v>-25.3523694578396</v>
       </c>
       <c r="F38">
-        <v>5.269419687482138</v>
+        <v>5.003669484255223</v>
       </c>
       <c r="G38">
-        <v>-7.988647931669909</v>
+        <v>-3.067458711928487</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.353063774613541</v>
       </c>
       <c r="E39">
-        <v>-27.2668724140624</v>
+        <v>-24.25693159538414</v>
       </c>
       <c r="F39">
-        <v>5.103042094629857</v>
+        <v>4.76305029129444</v>
       </c>
       <c r="G39">
-        <v>-7.317687341086857</v>
+        <v>-3.790249478264528</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.138233962572092</v>
       </c>
       <c r="E40">
-        <v>-26.78354838322374</v>
+        <v>-24.05097659751529</v>
       </c>
       <c r="F40">
-        <v>5.248453708517283</v>
+        <v>4.607764537965644</v>
       </c>
       <c r="G40">
-        <v>-7.259212691675993</v>
+        <v>-4.778317164016997</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.970264619268458</v>
       </c>
       <c r="E41">
-        <v>-25.74903208159347</v>
+        <v>-23.88305172436286</v>
       </c>
       <c r="F41">
-        <v>5.030934368950966</v>
+        <v>4.524324746216456</v>
       </c>
       <c r="G41">
-        <v>-7.381434913543749</v>
+        <v>-3.848871782645567</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.839190870215931</v>
       </c>
       <c r="E42">
-        <v>-25.74045968029695</v>
+        <v>-23.73796394563111</v>
       </c>
       <c r="F42">
-        <v>5.031028802834885</v>
+        <v>4.73623935193543</v>
       </c>
       <c r="G42">
-        <v>-7.751737172634882</v>
+        <v>-3.837876409199868</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.740942905397035</v>
       </c>
       <c r="E43">
-        <v>-25.01527890965663</v>
+        <v>-22.47000028043142</v>
       </c>
       <c r="F43">
-        <v>5.118867225492939</v>
+        <v>4.99277645290841</v>
       </c>
       <c r="G43">
-        <v>-7.402175515020999</v>
+        <v>-3.449832585136817</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.671545211759548</v>
       </c>
       <c r="E44">
-        <v>-23.81524688304601</v>
+        <v>-22.75688816576536</v>
       </c>
       <c r="F44">
-        <v>5.274411429451408</v>
+        <v>4.796910637251272</v>
       </c>
       <c r="G44">
-        <v>-7.577986647397606</v>
+        <v>-2.839728810816786</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.617551455070241</v>
       </c>
       <c r="E45">
-        <v>-24.97932282603573</v>
+        <v>-22.96312392902268</v>
       </c>
       <c r="F45">
-        <v>5.078785840341082</v>
+        <v>5.136329210343953</v>
       </c>
       <c r="G45">
-        <v>-7.743386463766095</v>
+        <v>-3.275117380761065</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.580669113656502</v>
       </c>
       <c r="E46">
-        <v>-24.16176118563894</v>
+        <v>-22.20470415916606</v>
       </c>
       <c r="F46">
-        <v>4.885272588107895</v>
+        <v>4.776973490600693</v>
       </c>
       <c r="G46">
-        <v>-8.016206911547686</v>
+        <v>-3.683737745223393</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.55025890914692</v>
       </c>
       <c r="E47">
-        <v>-23.72082819998608</v>
+        <v>-21.31157134452927</v>
       </c>
       <c r="F47">
-        <v>5.062515047815294</v>
+        <v>4.366939909888966</v>
       </c>
       <c r="G47">
-        <v>-7.917862138968008</v>
+        <v>-3.87876042983055</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.525859027818116</v>
       </c>
       <c r="E48">
-        <v>-22.95542552320964</v>
+        <v>-20.91261731292752</v>
       </c>
       <c r="F48">
-        <v>5.246919572087298</v>
+        <v>4.387276329627694</v>
       </c>
       <c r="G48">
-        <v>-7.905265529401301</v>
+        <v>-4.778937314891731</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.508161227190667</v>
       </c>
       <c r="E49">
-        <v>-22.18953829971437</v>
+        <v>-20.66138210345598</v>
       </c>
       <c r="F49">
-        <v>4.903753464864352</v>
+        <v>4.722678977551602</v>
       </c>
       <c r="G49">
-        <v>-8.532667903782725</v>
+        <v>-4.139489576165586</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.494293246698942</v>
       </c>
       <c r="E50">
-        <v>-21.26944747930992</v>
+        <v>-20.04315030345481</v>
       </c>
       <c r="F50">
-        <v>5.055217130996631</v>
+        <v>4.548831167460876</v>
       </c>
       <c r="G50">
-        <v>-8.141438013585452</v>
+        <v>-4.50174956121452</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.496803810749955</v>
       </c>
       <c r="E51">
-        <v>-21.52156121273895</v>
+        <v>-19.81794023410535</v>
       </c>
       <c r="F51">
-        <v>5.237365182463408</v>
+        <v>4.58891752281715</v>
       </c>
       <c r="G51">
-        <v>-7.818201596542994</v>
+        <v>-3.985288568979481</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.51724418095758</v>
       </c>
       <c r="E52">
-        <v>-21.47911582586506</v>
+        <v>-19.70291246583652</v>
       </c>
       <c r="F52">
-        <v>5.25430860932027</v>
+        <v>4.611175754930373</v>
       </c>
       <c r="G52">
-        <v>-8.377082221098535</v>
+        <v>-3.994784424172515</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.569162837688423</v>
       </c>
       <c r="E53">
-        <v>-20.80115798217673</v>
+        <v>-18.44571298335306</v>
       </c>
       <c r="F53">
-        <v>5.270546267149945</v>
+        <v>4.63294690701075</v>
       </c>
       <c r="G53">
-        <v>-8.892096194625857</v>
+        <v>-4.705273890882197</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.661974205108871</v>
       </c>
       <c r="E54">
-        <v>-20.94502760140042</v>
+        <v>-17.50879888201011</v>
       </c>
       <c r="F54">
-        <v>5.328187384506347</v>
+        <v>4.649285625663567</v>
       </c>
       <c r="G54">
-        <v>-8.429069895486377</v>
+        <v>-4.729876490134914</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.800078625942898</v>
       </c>
       <c r="E55">
-        <v>-19.99292046976173</v>
+        <v>-18.53760477791671</v>
       </c>
       <c r="F55">
-        <v>5.287362125426776</v>
+        <v>4.662229694699712</v>
       </c>
       <c r="G55">
-        <v>-8.674347769497988</v>
+        <v>-5.494532362347911</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.997643251736124</v>
       </c>
       <c r="E56">
-        <v>-19.50647179185778</v>
+        <v>-16.69562080445274</v>
       </c>
       <c r="F56">
-        <v>5.22381640522322</v>
+        <v>4.408229054714105</v>
       </c>
       <c r="G56">
-        <v>-8.626504277939723</v>
+        <v>-5.700035268615934</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.249240337160515</v>
       </c>
       <c r="E57">
-        <v>-19.40879713598634</v>
+        <v>-18.43390272314106</v>
       </c>
       <c r="F57">
-        <v>5.601266982513232</v>
+        <v>4.550434886752696</v>
       </c>
       <c r="G57">
-        <v>-8.691308403738757</v>
+        <v>-4.810565009503219</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.560511655144457</v>
       </c>
       <c r="E58">
-        <v>-19.15671963034937</v>
+        <v>-17.00615638105473</v>
       </c>
       <c r="F58">
-        <v>5.652474998619491</v>
+        <v>4.511344229014587</v>
       </c>
       <c r="G58">
-        <v>-8.816555911884322</v>
+        <v>-6.160971429622049</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.923969835846691</v>
       </c>
       <c r="E59">
-        <v>-18.60465789254829</v>
+        <v>-16.48006544168764</v>
       </c>
       <c r="F59">
-        <v>5.488430088373494</v>
+        <v>4.911082859644322</v>
       </c>
       <c r="G59">
-        <v>-9.223857225279753</v>
+        <v>-5.822342802244235</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.324884061200234</v>
       </c>
       <c r="E60">
-        <v>-18.25098860102324</v>
+        <v>-15.82214609548325</v>
       </c>
       <c r="F60">
-        <v>5.462846789505434</v>
+        <v>4.87518970008102</v>
       </c>
       <c r="G60">
-        <v>-9.099689239027247</v>
+        <v>-5.922974586250845</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.754176714316007</v>
       </c>
       <c r="E61">
-        <v>-18.14728654624759</v>
+        <v>-16.80885076854053</v>
       </c>
       <c r="F61">
-        <v>5.856230185420891</v>
+        <v>4.643535099153333</v>
       </c>
       <c r="G61">
-        <v>-9.517903895329392</v>
+        <v>-5.854367524664416</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.184152892616011</v>
       </c>
       <c r="E62">
-        <v>-17.80895972466053</v>
+        <v>-14.15294151930794</v>
       </c>
       <c r="F62">
-        <v>5.71547730980681</v>
+        <v>5.333657922834434</v>
       </c>
       <c r="G62">
-        <v>-9.372145471215738</v>
+        <v>-5.99964689043039</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.60699709163213</v>
       </c>
       <c r="E63">
-        <v>-18.03429206280819</v>
+        <v>-16.23078653298741</v>
       </c>
       <c r="F63">
-        <v>5.763998102058388</v>
+        <v>5.083739477409823</v>
       </c>
       <c r="G63">
-        <v>-9.435286017684133</v>
+        <v>-6.023124030688217</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.006048791871628</v>
       </c>
       <c r="E64">
-        <v>-17.81584753362619</v>
+        <v>-15.79530130156578</v>
       </c>
       <c r="F64">
-        <v>5.566223727905201</v>
+        <v>5.325415667176579</v>
       </c>
       <c r="G64">
-        <v>-9.718662155222457</v>
+        <v>-6.757349854158923</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.369147761165965</v>
       </c>
       <c r="E65">
-        <v>-18.22749940634545</v>
+        <v>-15.78902936506515</v>
       </c>
       <c r="F65">
-        <v>5.652629074956412</v>
+        <v>4.62817716750543</v>
       </c>
       <c r="G65">
-        <v>-9.578340715232804</v>
+        <v>-7.201709283846724</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.694236162383515</v>
       </c>
       <c r="E66">
-        <v>-17.90456939638447</v>
+        <v>-14.08970137979082</v>
       </c>
       <c r="F66">
-        <v>5.825878803782317</v>
+        <v>4.833378683792118</v>
       </c>
       <c r="G66">
-        <v>-9.866950401158443</v>
+        <v>-7.141725272518515</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.964240863711292</v>
       </c>
       <c r="E67">
-        <v>-18.04119798566989</v>
+        <v>-15.77037205215355</v>
       </c>
       <c r="F67">
-        <v>5.570126995107192</v>
+        <v>4.507165943834867</v>
       </c>
       <c r="G67">
-        <v>-10.57862438885108</v>
+        <v>-6.357841441967172</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.177641968301565</v>
       </c>
       <c r="E68">
-        <v>-17.38697387425576</v>
+        <v>-16.41237381222098</v>
       </c>
       <c r="F68">
-        <v>5.691103427346838</v>
+        <v>4.812298390125676</v>
       </c>
       <c r="G68">
-        <v>-9.674674098996542</v>
+        <v>-7.405309081610269</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.322109649349722</v>
       </c>
       <c r="E69">
-        <v>-18.25670353522092</v>
+        <v>-15.08011487306039</v>
       </c>
       <c r="F69">
-        <v>5.564651486574688</v>
+        <v>4.46411071970696</v>
       </c>
       <c r="G69">
-        <v>-9.676409865201487</v>
+        <v>-6.107933764335185</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.391994162641568</v>
       </c>
       <c r="E70">
-        <v>-17.02557447759962</v>
+        <v>-15.14147569586432</v>
       </c>
       <c r="F70">
-        <v>5.626321782978305</v>
+        <v>4.474124024872</v>
       </c>
       <c r="G70">
-        <v>-9.425609695305331</v>
+        <v>-7.044643770239224</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.388734182953094</v>
       </c>
       <c r="E71">
-        <v>-16.78708692245967</v>
+        <v>-14.43544584180245</v>
       </c>
       <c r="F71">
-        <v>5.116219763273592</v>
+        <v>4.671126360605778</v>
       </c>
       <c r="G71">
-        <v>-9.403776447048786</v>
+        <v>-6.6264192702724</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.303774716311468</v>
       </c>
       <c r="E72">
-        <v>-16.87300113133319</v>
+        <v>-15.16432184723302</v>
       </c>
       <c r="F72">
-        <v>5.072288126433523</v>
+        <v>4.364560838708126</v>
       </c>
       <c r="G72">
-        <v>-9.51011427534727</v>
+        <v>-6.648856263295883</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.147006744563509</v>
       </c>
       <c r="E73">
-        <v>-17.12107093747337</v>
+        <v>-14.72904039714174</v>
       </c>
       <c r="F73">
-        <v>4.962632163120536</v>
+        <v>4.119627508313563</v>
       </c>
       <c r="G73">
-        <v>-9.209072040932895</v>
+        <v>-6.518437549972634</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.917938242603906</v>
       </c>
       <c r="E74">
-        <v>-16.70942359322812</v>
+        <v>-15.63288758128068</v>
       </c>
       <c r="F74">
-        <v>5.030516871779955</v>
+        <v>3.895366914823264</v>
       </c>
       <c r="G74">
-        <v>-9.066673587696114</v>
+        <v>-5.943321441140962</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.624998664586546</v>
       </c>
       <c r="E75">
-        <v>-16.74077874725723</v>
+        <v>-13.99192709749121</v>
       </c>
       <c r="F75">
-        <v>4.998374559816528</v>
+        <v>4.003506965789128</v>
       </c>
       <c r="G75">
-        <v>-8.65548402675274</v>
+        <v>-6.560611090676177</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.280737920895843</v>
       </c>
       <c r="E76">
-        <v>-17.74031258717825</v>
+        <v>-14.37970938371604</v>
       </c>
       <c r="F76">
-        <v>4.909412870960279</v>
+        <v>3.506090564490886</v>
       </c>
       <c r="G76">
-        <v>-8.4728873281912</v>
+        <v>-5.586130943401369</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.888181840424768</v>
       </c>
       <c r="E77">
-        <v>-17.93018244537185</v>
+        <v>-14.9450395503596</v>
       </c>
       <c r="F77">
-        <v>4.687774888667243</v>
+        <v>3.923895888175679</v>
       </c>
       <c r="G77">
-        <v>-7.986236233823718</v>
+        <v>-5.417374437377569</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.467171513125851</v>
       </c>
       <c r="E78">
-        <v>-17.50083329623062</v>
+        <v>-16.29383194812219</v>
       </c>
       <c r="F78">
-        <v>4.714768068854868</v>
+        <v>3.760341371432139</v>
       </c>
       <c r="G78">
-        <v>-8.32327018752364</v>
+        <v>-5.602710955941244</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.022751755166147</v>
       </c>
       <c r="E79">
-        <v>-19.14486408539729</v>
+        <v>-16.40463012166786</v>
       </c>
       <c r="F79">
-        <v>4.457661051108762</v>
+        <v>3.38052166337012</v>
       </c>
       <c r="G79">
-        <v>-8.412457070730907</v>
+        <v>-5.493462684119532</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.568456266227445</v>
       </c>
       <c r="E80">
-        <v>-18.91334585175514</v>
+        <v>-16.14444211908316</v>
       </c>
       <c r="F80">
-        <v>4.075062998777755</v>
+        <v>3.690210130376327</v>
       </c>
       <c r="G80">
-        <v>-7.361245557288485</v>
+        <v>-5.236234601188423</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.116553009681535</v>
       </c>
       <c r="E81">
-        <v>-19.64229431276984</v>
+        <v>-16.9932683440289</v>
       </c>
       <c r="F81">
-        <v>4.170310339486448</v>
+        <v>3.343839898039353</v>
       </c>
       <c r="G81">
-        <v>-6.9736414169144</v>
+        <v>-4.704706239552414</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.669626283122485</v>
       </c>
       <c r="E82">
-        <v>-20.37558558035789</v>
+        <v>-17.28160534104529</v>
       </c>
       <c r="F82">
-        <v>4.143194560923209</v>
+        <v>3.390866315496281</v>
       </c>
       <c r="G82">
-        <v>-6.913096316699526</v>
+        <v>-4.952494248057</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.243996128828961</v>
       </c>
       <c r="E83">
-        <v>-21.00851227851395</v>
+        <v>-17.96546831483962</v>
       </c>
       <c r="F83">
-        <v>3.844306348114702</v>
+        <v>3.462033015805592</v>
       </c>
       <c r="G83">
-        <v>-6.966855850729468</v>
+        <v>-5.489695841769289</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.839299030632083</v>
       </c>
       <c r="E84">
-        <v>-21.65245222545666</v>
+        <v>-19.27229534397313</v>
       </c>
       <c r="F84">
-        <v>3.598577785013451</v>
+        <v>3.142286511794594</v>
       </c>
       <c r="G84">
-        <v>-6.345737015634381</v>
+        <v>-4.585998205974823</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.463735071273289</v>
       </c>
       <c r="E85">
-        <v>-22.39615898326235</v>
+        <v>-19.17371046482615</v>
       </c>
       <c r="F85">
-        <v>3.300559357977884</v>
+        <v>2.178736175797432</v>
       </c>
       <c r="G85">
-        <v>-5.824304972736783</v>
+        <v>-4.015170653721345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.120778047563819</v>
       </c>
       <c r="E86">
-        <v>-23.5132565368965</v>
+        <v>-21.11998066621275</v>
       </c>
       <c r="F86">
-        <v>3.118699578367281</v>
+        <v>1.972416363516964</v>
       </c>
       <c r="G86">
-        <v>-5.863203854324</v>
+        <v>-4.022507465128263</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.807995742794604</v>
       </c>
       <c r="E87">
-        <v>-25.04172519786143</v>
+        <v>-22.45315435712289</v>
       </c>
       <c r="F87">
-        <v>3.144564522152293</v>
+        <v>1.906652275408712</v>
       </c>
       <c r="G87">
-        <v>-5.253201797872311</v>
+        <v>-3.852897841499006</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.533525742177599</v>
       </c>
       <c r="E88">
-        <v>-25.58163703989993</v>
+        <v>-24.03410350336271</v>
       </c>
       <c r="F88">
-        <v>2.589886395768132</v>
+        <v>1.562977550600447</v>
       </c>
       <c r="G88">
-        <v>-5.11032756750941</v>
+        <v>-2.818811023375326</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.292339440183931</v>
       </c>
       <c r="E89">
-        <v>-28.18532845535008</v>
+        <v>-24.33794599538136</v>
       </c>
       <c r="F89">
-        <v>2.59279727882157</v>
+        <v>1.729782581032572</v>
       </c>
       <c r="G89">
-        <v>-4.910878515018563</v>
+        <v>-2.744081202358972</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.089703541211787</v>
       </c>
       <c r="E90">
-        <v>-28.86615282308527</v>
+        <v>-26.60540727271</v>
       </c>
       <c r="F90">
-        <v>2.120453902071264</v>
+        <v>1.605843906960516</v>
       </c>
       <c r="G90">
-        <v>-4.299068505487621</v>
+        <v>-2.796459342112388</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.926524216333299</v>
       </c>
       <c r="E91">
-        <v>-30.31660493384605</v>
+        <v>-27.3094400697345</v>
       </c>
       <c r="F91">
-        <v>1.669959543937197</v>
+        <v>1.113207185576427</v>
       </c>
       <c r="G91">
-        <v>-4.122420661613354</v>
+        <v>-2.099390071580834</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.803051390810144</v>
       </c>
       <c r="E92">
-        <v>-32.55383864717349</v>
+        <v>-30.4981197574955</v>
       </c>
       <c r="F92">
-        <v>1.321301360833691</v>
+        <v>0.5274967595485922</v>
       </c>
       <c r="G92">
-        <v>-4.199457181385998</v>
+        <v>-2.909143052906839</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.727787138348676</v>
       </c>
       <c r="E93">
-        <v>-33.31503210735981</v>
+        <v>-31.4047179895941</v>
       </c>
       <c r="F93">
-        <v>0.7860782712716803</v>
+        <v>-0.1733799297556527</v>
       </c>
       <c r="G93">
-        <v>-4.290881857696806</v>
+        <v>-2.437762763677011</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.698398250802366</v>
       </c>
       <c r="E94">
-        <v>-36.41395291181477</v>
+        <v>-33.1631787884606</v>
       </c>
       <c r="F94">
-        <v>0.4430546432420162</v>
+        <v>0.01396281369408071</v>
       </c>
       <c r="G94">
-        <v>-4.546633390926164</v>
+        <v>-2.786894581266607</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.719472350431158</v>
       </c>
       <c r="E95">
-        <v>-37.73328532192047</v>
+        <v>-36.46445671818532</v>
       </c>
       <c r="F95">
-        <v>-0.2428426783174052</v>
+        <v>-0.4054122662190166</v>
       </c>
       <c r="G95">
-        <v>-3.951449331036928</v>
+        <v>-2.304246577201646</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.790433676474495</v>
       </c>
       <c r="E96">
-        <v>-38.80134403052556</v>
+        <v>-38.81177763463923</v>
       </c>
       <c r="F96">
-        <v>-0.5398620942651959</v>
+        <v>-1.073854229866647</v>
       </c>
       <c r="G96">
-        <v>-4.310047472825523</v>
+        <v>-2.867566694527115</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.9025021719057</v>
       </c>
       <c r="E97">
-        <v>-41.2572577536834</v>
+        <v>-40.96602932601311</v>
       </c>
       <c r="F97">
-        <v>-0.8981840114897613</v>
+        <v>-0.8803782541665859</v>
       </c>
       <c r="G97">
-        <v>-4.174109744839288</v>
+        <v>-2.72926648701808</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.059329796811117</v>
       </c>
       <c r="E98">
-        <v>-44.03427651177713</v>
+        <v>-42.96511059127717</v>
       </c>
       <c r="F98">
-        <v>-1.564611385613783</v>
+        <v>-2.05854947218767</v>
       </c>
       <c r="G98">
-        <v>-4.804311001210918</v>
+        <v>-2.474135104663456</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.238212883548456</v>
       </c>
       <c r="E99">
-        <v>-45.4485280013206</v>
+        <v>-45.52252779507994</v>
       </c>
       <c r="F99">
-        <v>-1.991414436027784</v>
+        <v>-2.328130874652532</v>
       </c>
       <c r="G99">
-        <v>-4.853466981392959</v>
+        <v>-3.051233071317033</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.448639780018702</v>
       </c>
       <c r="E100">
-        <v>-48.27566564549422</v>
+        <v>-47.43324721126933</v>
       </c>
       <c r="F100">
-        <v>-2.438119841661445</v>
+        <v>-2.688112840152308</v>
       </c>
       <c r="G100">
-        <v>-5.165724431097515</v>
+        <v>-2.911410377004415</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.650546600346783</v>
       </c>
       <c r="E101">
-        <v>-50.59286315284911</v>
+        <v>-49.21668028005111</v>
       </c>
       <c r="F101">
-        <v>-2.813210400220881</v>
+        <v>-3.042018730752549</v>
       </c>
       <c r="G101">
-        <v>-5.193877312077551</v>
+        <v>-3.013279181538936</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.875399880037887</v>
       </c>
       <c r="E102">
-        <v>-52.88809642914828</v>
+        <v>-52.65525927745141</v>
       </c>
       <c r="F102">
-        <v>-2.952334705521058</v>
+        <v>-2.676945619195167</v>
       </c>
       <c r="G102">
-        <v>-5.459626727398538</v>
+        <v>-3.451761943413771</v>
       </c>
     </row>
   </sheetData>
